--- a/jira_export_2026-10-07.xlsx
+++ b/jira_export_2026-10-07.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>99 h</t>
+          <t>102 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P131"/>
+  <dimension ref="A1:P132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1669,7 +1669,7 @@
         <v>1</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>3.25</v>
+        <v>5.25</v>
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         <v>4</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
@@ -7549,7 +7549,7 @@
         <v>9</v>
       </c>
       <c r="K95" s="11" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="L95" s="11" t="inlineStr">
         <is>
@@ -9444,22 +9444,22 @@
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-13280</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[Arles] Littéralis Prime</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>[Arles]</t>
         </is>
       </c>
       <c r="E123" s="11" t="n">
@@ -9475,17 +9475,21 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H123" s="11" t="inlineStr"/>
+      <c r="H123" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I123" s="11" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>10/11/2023</t>
         </is>
       </c>
       <c r="J123" s="11" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K123" s="11" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L123" s="11" t="inlineStr"/>
       <c r="M123" s="11" t="inlineStr"/>
@@ -9502,12 +9506,12 @@
     <row r="124">
       <c r="A124" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B124" s="15" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C124" s="15" t="inlineStr">
@@ -9517,7 +9521,7 @@
       </c>
       <c r="D124" s="15" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E124" s="15" t="n">
@@ -9533,32 +9537,20 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H124" s="15" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H124" s="15" t="inlineStr"/>
       <c r="I124" s="15" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J124" s="15" t="n">
         <v>37</v>
       </c>
       <c r="K124" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="L124" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M124" s="15" t="inlineStr">
-        <is>
-          <t>412263</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L124" s="15" t="inlineStr"/>
+      <c r="M124" s="15" t="inlineStr"/>
       <c r="N124" s="16" t="n">
         <v>0</v>
       </c>
@@ -9572,22 +9564,22 @@
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12292</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>[CD06] Littéralis expert</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
+          <t>LE MANS METROPOLE</t>
         </is>
       </c>
       <c r="E125" s="11" t="n">
@@ -9600,29 +9592,33 @@
       </c>
       <c r="G125" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H125" s="11" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H125" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I125" s="11" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J125" s="11" t="n">
         <v>37</v>
       </c>
       <c r="K125" s="11" t="n">
-        <v>0.75</v>
+        <v>5</v>
       </c>
       <c r="L125" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-25456</t>
+          <t>PDMDEP-34532</t>
         </is>
       </c>
       <c r="M125" s="11" t="inlineStr">
         <is>
-          <t>424152</t>
+          <t>412263</t>
         </is>
       </c>
       <c r="N125" s="12" t="n">
@@ -9638,24 +9634,26 @@
     <row r="126">
       <c r="A126" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12292</t>
         </is>
       </c>
       <c r="B126" s="15" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C126" s="15" t="inlineStr"/>
+          <t>[CD06] Littéralis expert</t>
+        </is>
+      </c>
+      <c r="C126" s="15" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D126" s="15" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E126" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
+        </is>
+      </c>
+      <c r="E126" s="15" t="n">
+        <v/>
       </c>
       <c r="F126" s="15" t="inlineStr">
         <is>
@@ -9664,27 +9662,31 @@
       </c>
       <c r="G126" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H126" s="15" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H126" s="15" t="inlineStr"/>
       <c r="I126" s="15" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J126" s="15" t="n">
         <v>37</v>
       </c>
       <c r="K126" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L126" s="15" t="inlineStr"/>
-      <c r="M126" s="15" t="inlineStr"/>
+        <v>0.75</v>
+      </c>
+      <c r="L126" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-25456</t>
+        </is>
+      </c>
+      <c r="M126" s="15" t="inlineStr">
+        <is>
+          <t>424152</t>
+        </is>
+      </c>
       <c r="N126" s="16" t="n">
         <v>0</v>
       </c>
@@ -9698,21 +9700,25 @@
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>PSC-1339</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C127" s="11" t="inlineStr"/>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
-        </is>
-      </c>
-      <c r="E127" s="11" t="inlineStr"/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E127" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
       <c r="F127" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -9720,35 +9726,31 @@
       </c>
       <c r="G127" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H127" s="11" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H127" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I127" s="11" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J127" s="11" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="K127" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L127" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-35312</t>
-        </is>
-      </c>
-      <c r="M127" s="11" t="inlineStr">
-        <is>
-          <t>00177354</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L127" s="11" t="inlineStr"/>
+      <c r="M127" s="11" t="inlineStr"/>
       <c r="N127" s="12" t="n">
-        <v>450</v>
-      </c>
-      <c r="O127" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P127" s="12" t="n">
@@ -9758,18 +9760,18 @@
     <row r="128">
       <c r="A128" s="14" t="inlineStr">
         <is>
-          <t>PSC-1288</t>
+          <t>PSC-1339</t>
         </is>
       </c>
       <c r="B128" s="15" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="C128" s="15" t="inlineStr"/>
       <c r="D128" s="15" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="E128" s="15" t="inlineStr"/>
@@ -9780,27 +9782,35 @@
       </c>
       <c r="G128" s="15" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H128" s="15" t="inlineStr"/>
       <c r="I128" s="15" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J128" s="15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K128" s="15" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="L128" s="15" t="inlineStr"/>
-      <c r="M128" s="15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L128" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-35312</t>
+        </is>
+      </c>
+      <c r="M128" s="15" t="inlineStr">
+        <is>
+          <t>00177354</t>
+        </is>
+      </c>
       <c r="N128" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O128" s="16" t="n">
+        <v>450</v>
+      </c>
+      <c r="O128" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P128" s="16" t="n">
@@ -9810,18 +9820,18 @@
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1288</t>
         </is>
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="C129" s="11" t="inlineStr"/>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="E129" s="11" t="inlineStr"/>
@@ -9832,31 +9842,23 @@
       </c>
       <c r="G129" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H129" s="11" t="inlineStr"/>
       <c r="I129" s="11" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J129" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K129" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L129" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M129" s="11" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+        <v>0.08</v>
+      </c>
+      <c r="L129" s="11" t="inlineStr"/>
+      <c r="M129" s="11" t="inlineStr"/>
       <c r="N129" s="12" t="n">
         <v>0</v>
       </c>
@@ -9870,18 +9872,18 @@
     <row r="130">
       <c r="A130" s="14" t="inlineStr">
         <is>
-          <t>PSC-1047</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B130" s="15" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C130" s="15" t="inlineStr"/>
       <c r="D130" s="15" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E130" s="15" t="inlineStr"/>
@@ -9898,61 +9900,121 @@
       <c r="H130" s="15" t="inlineStr"/>
       <c r="I130" s="15" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="J130" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="K130" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L130" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M130" s="15" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
+      <c r="N130" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O130" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P130" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="10" t="inlineStr">
+        <is>
+          <t>PSC-1047</t>
+        </is>
+      </c>
+      <c r="B131" s="11" t="inlineStr">
+        <is>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+        </is>
+      </c>
+      <c r="C131" s="11" t="inlineStr"/>
+      <c r="D131" s="11" t="inlineStr">
+        <is>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E131" s="11" t="inlineStr"/>
+      <c r="F131" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G131" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H131" s="11" t="inlineStr"/>
+      <c r="I131" s="11" t="inlineStr">
+        <is>
           <t>04/11/2025</t>
         </is>
       </c>
-      <c r="J130" s="15" t="n">
+      <c r="J131" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="K130" s="15" t="n">
+      <c r="K131" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="L130" s="15" t="inlineStr">
+      <c r="L131" s="11" t="inlineStr">
         <is>
           <t>PDMDEP-26768</t>
         </is>
       </c>
-      <c r="M130" s="15" t="inlineStr">
+      <c r="M131" s="11" t="inlineStr">
         <is>
           <t>00141775</t>
         </is>
       </c>
-      <c r="N130" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O130" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P130" s="16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="17" t="inlineStr">
+      <c r="N131" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O131" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P131" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B131" s="17" t="inlineStr"/>
-      <c r="C131" s="17" t="inlineStr"/>
-      <c r="D131" s="17" t="inlineStr"/>
-      <c r="E131" s="17" t="inlineStr"/>
-      <c r="F131" s="17" t="inlineStr"/>
-      <c r="G131" s="17" t="inlineStr"/>
-      <c r="H131" s="17" t="inlineStr"/>
-      <c r="I131" s="17" t="inlineStr"/>
-      <c r="J131" s="17" t="inlineStr"/>
-      <c r="K131" s="17" t="inlineStr"/>
-      <c r="L131" s="17" t="inlineStr"/>
-      <c r="M131" s="17" t="inlineStr"/>
-      <c r="N131" s="18" t="n">
+      <c r="B132" s="17" t="inlineStr"/>
+      <c r="C132" s="17" t="inlineStr"/>
+      <c r="D132" s="17" t="inlineStr"/>
+      <c r="E132" s="17" t="inlineStr"/>
+      <c r="F132" s="17" t="inlineStr"/>
+      <c r="G132" s="17" t="inlineStr"/>
+      <c r="H132" s="17" t="inlineStr"/>
+      <c r="I132" s="17" t="inlineStr"/>
+      <c r="J132" s="17" t="inlineStr"/>
+      <c r="K132" s="17" t="inlineStr"/>
+      <c r="L132" s="17" t="inlineStr"/>
+      <c r="M132" s="17" t="inlineStr"/>
+      <c r="N132" s="18" t="n">
         <v>122424.762</v>
       </c>
-      <c r="O131" s="18" t="n">
+      <c r="O132" s="18" t="n">
         <v>2445.3</v>
       </c>
-      <c r="P131" s="18" t="n">
-        <v>39.7</v>
+      <c r="P132" s="18" t="n">
+        <v>37.71</v>
       </c>
     </row>
   </sheetData>
@@ -10084,6 +10146,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId124"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId125"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A130" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A131" r:id="rId127"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10841,16 +10904,16 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>37.5</v>
+        <v>40.25</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>1.08</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>48.58</v>
+        <v>51.83</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>6.75</v>
@@ -10860,7 +10923,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>10.2%</t>
         </is>
       </c>
     </row>

--- a/jira_export_2026-10-07.xlsx
+++ b/jira_export_2026-10-07.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>102 h</t>
+          <t>105 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -7549,7 +7549,7 @@
         <v>9</v>
       </c>
       <c r="K95" s="11" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="L95" s="11" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>11</v>
       </c>
       <c r="K98" s="15" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="L98" s="15" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         <v>11</v>
       </c>
       <c r="K99" s="11" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="L99" s="11" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>11</v>
       </c>
       <c r="K100" s="15" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="L100" s="15" t="inlineStr">
         <is>
@@ -7977,7 +7977,7 @@
         <v>11</v>
       </c>
       <c r="K101" s="11" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="L101" s="11" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>11</v>
       </c>
       <c r="K102" s="15" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="L102" s="15" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>2445.3</v>
       </c>
       <c r="P132" s="18" t="n">
-        <v>37.71</v>
+        <v>36.72</v>
       </c>
     </row>
   </sheetData>
@@ -10904,7 +10904,7 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>40.25</v>
+        <v>42</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>10.5</v>
@@ -10913,7 +10913,7 @@
         <v>1.08</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>51.83</v>
+        <v>53.58</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>6.75</v>
@@ -10923,7 +10923,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.5%</t>
         </is>
       </c>
     </row>
@@ -10965,7 +10965,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>29.08</v>
+        <v>30.08</v>
       </c>
     </row>
   </sheetData>
@@ -11050,10 +11050,10 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>502435</v>
+        <v>507682</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>202932</v>
+        <v>208179</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>299503</v>
@@ -11100,10 +11100,10 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>240255</v>
+        <v>245502</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>136970</v>
+        <v>142217</v>
       </c>
       <c r="D7" s="26" t="n">
         <v>103284</v>
@@ -11337,7 +11337,7 @@
         </is>
       </c>
       <c r="I7" s="25" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="8">
@@ -11804,7 +11804,7 @@
         </is>
       </c>
       <c r="I18" s="24" t="n">
-        <v>8028</v>
+        <v>9828</v>
       </c>
     </row>
     <row r="19">
@@ -11846,7 +11846,7 @@
         </is>
       </c>
       <c r="I20" s="24" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
     </row>
   </sheetData>

--- a/jira_export_2026-10-07.xlsx
+++ b/jira_export_2026-10-07.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>105 h</t>
+          <t>109 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>288</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -3525,7 +3525,7 @@
         <v>4</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>5</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>5</v>
       </c>
       <c r="K66" s="15" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L66" s="15" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>2445.3</v>
       </c>
       <c r="P132" s="18" t="n">
-        <v>36.72</v>
+        <v>35.14</v>
       </c>
     </row>
   </sheetData>
@@ -10158,7 +10158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -10166,7 +10166,7 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
@@ -10184,7 +10184,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tickets 'Matériel GEODP' clôturés ce mois — 3 ligne(s)</t>
+          <t>Tickets 'Matériel GEODP' clôturés ce mois — 4 ligne(s)</t>
         </is>
       </c>
     </row>
@@ -10249,22 +10249,22 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34012</t>
+          <t>PDMDEP-34287</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE BIARRITZ] - Migration module Placier</t>
+          <t xml:space="preserve">[COMMUNE DE LUNEL] - Migration GeODP </t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>COMMUNE DE LUNEL</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>Migration module Placier</t>
+          <t xml:space="preserve">Migration GeODP </t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="G5" s="11" t="inlineStr">
@@ -10287,12 +10287,12 @@
       </c>
       <c r="I5" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34019</t>
+          <t>PDMDEP-34294</t>
         </is>
       </c>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>00170492</t>
+          <t>00171435</t>
         </is>
       </c>
       <c r="K5" s="12" t="n">
@@ -10302,22 +10302,22 @@
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31812</t>
+          <t>PDMDEP-34012</t>
         </is>
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
+          <t>[COMMUNE DE BIARRITZ] - Migration module Placier</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE PROVINS</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>Migration module Placier</t>
         </is>
       </c>
       <c r="E6" s="15" t="inlineStr">
@@ -10340,37 +10340,37 @@
       </c>
       <c r="I6" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31819</t>
+          <t>PDMDEP-34019</t>
         </is>
       </c>
       <c r="J6" s="15" t="inlineStr">
         <is>
-          <t>00159472</t>
+          <t>00170492</t>
         </is>
       </c>
       <c r="K6" s="16" t="n">
-        <v>815</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31479</t>
+          <t>PDMDEP-31812</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 </t>
+          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE TREGUIER</t>
+          <t>COMMUNE PROVINS</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
@@ -10393,12 +10393,12 @@
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31486</t>
+          <t>PDMDEP-31819</t>
         </is>
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>00157474</t>
+          <t>00159472</t>
         </is>
       </c>
       <c r="K7" s="12" t="n">
@@ -10406,22 +10406,75 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-31479</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 </t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>COMMUNE DE TREGUIER</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Migration vers GeoDP V2</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-31486</t>
+        </is>
+      </c>
+      <c r="J8" s="15" t="inlineStr">
+        <is>
+          <t>00157474</t>
+        </is>
+      </c>
+      <c r="K8" s="16" t="n">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr"/>
-      <c r="C8" s="17" t="inlineStr"/>
-      <c r="D8" s="17" t="inlineStr"/>
-      <c r="E8" s="17" t="inlineStr"/>
-      <c r="F8" s="17" t="inlineStr"/>
-      <c r="G8" s="17" t="inlineStr"/>
-      <c r="H8" s="17" t="inlineStr"/>
-      <c r="I8" s="17" t="inlineStr"/>
-      <c r="J8" s="17" t="inlineStr"/>
-      <c r="K8" s="18" t="n">
-        <v>3260</v>
+      <c r="B9" s="17" t="inlineStr"/>
+      <c r="C9" s="17" t="inlineStr"/>
+      <c r="D9" s="17" t="inlineStr"/>
+      <c r="E9" s="17" t="inlineStr"/>
+      <c r="F9" s="17" t="inlineStr"/>
+      <c r="G9" s="17" t="inlineStr"/>
+      <c r="H9" s="17" t="inlineStr"/>
+      <c r="I9" s="17" t="inlineStr"/>
+      <c r="J9" s="17" t="inlineStr"/>
+      <c r="K9" s="18" t="n">
+        <v>4890</v>
       </c>
     </row>
   </sheetData>
@@ -10430,6 +10483,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10904,7 +10958,7 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>10.5</v>
@@ -10913,17 +10967,17 @@
         <v>1.08</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>53.58</v>
+        <v>56.58</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>6.75</v>
+        <v>7.75</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>508.2</v>
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
@@ -11053,16 +11107,16 @@
         <v>507682</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>208179</v>
+        <v>213769</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>299503</v>
+        <v>293913</v>
       </c>
       <c r="E5" s="24" t="n">
         <v>227001</v>
       </c>
       <c r="F5" s="24" t="n">
-        <v>27141</v>
+        <v>21551</v>
       </c>
       <c r="G5" s="24" t="n">
         <v>18055</v>
@@ -11100,19 +11154,19 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>245502</v>
+        <v>242402</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>142217</v>
+        <v>144707</v>
       </c>
       <c r="D7" s="26" t="n">
-        <v>103284</v>
+        <v>97694</v>
       </c>
       <c r="E7" s="26" t="n">
         <v>50106</v>
       </c>
       <c r="F7" s="26" t="n">
-        <v>17966</v>
+        <v>12376</v>
       </c>
       <c r="G7" s="26" t="n">
         <v>10431</v>
